--- a/testdata/TestData.xlsx
+++ b/testdata/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TESTING\Selenium_Workspace\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF69FB1-29F9-4F0D-92B4-63AA6CA8D522}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F53947-7818-42EB-930E-BACDD0CA6F9E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,6 @@
     <t>http://localhost/login.do</t>
   </si>
   <si>
-    <t>Chrome</t>
-  </si>
-  <si>
     <t>demo</t>
   </si>
   <si>
@@ -78,9 +75,6 @@
     <t>Mercury@1</t>
   </si>
   <si>
-    <t>Edge</t>
-  </si>
-  <si>
     <t>LogicalName</t>
   </si>
   <si>
@@ -94,6 +88,12 @@
   </si>
   <si>
     <t>manager</t>
+  </si>
+  <si>
+    <t>Firefox</t>
+  </si>
+  <si>
+    <t>edge</t>
   </si>
 </sst>
 </file>
@@ -456,7 +456,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -491,19 +491,19 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -514,37 +514,37 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
